--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2021_metropolitana.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2021_metropolitana.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:29</t>
+    <t xml:space="preserve">2026-09-24 01:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -852,13 +852,13 @@
         <v>50</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="15">
@@ -878,10 +878,10 @@
         <v>-0.03</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="16">
@@ -901,7 +901,7 @@
         <v>-0.11</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>-0.09</v>
@@ -921,13 +921,13 @@
         <v>46</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="18">
@@ -1013,13 +1013,13 @@
         <v>52</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="22">
@@ -1039,7 +1039,7 @@
         <v>-0.19</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>-0.22</v>
@@ -1062,7 +1062,7 @@
         <v>-0.11</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>-0.25</v>
@@ -1082,13 +1082,13 @@
         <v>52</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="25">
@@ -1108,10 +1108,10 @@
         <v>0.18</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="26">
@@ -1131,7 +1131,7 @@
         <v>0.25</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0.17</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2021_metropolitana.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2021_metropolitana.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:19</t>
+    <t xml:space="preserve">2026-10-01 23:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2021_metropolitana.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2021_metropolitana.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:19</t>
+    <t xml:space="preserve">2026-10-05 19:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
